--- a/Development/Common/GameData/Buff.xlsx
+++ b/Development/Common/GameData/Buff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBCA425-E5E9-4EEA-B019-D9C6234CC079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700A86C0-E9D7-47F3-BE72-758816BD88F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38730" yWindow="5985" windowWidth="27360" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3450" yWindow="3570" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buff" sheetId="1" r:id="rId1"/>
@@ -88,10 +88,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Buff</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -313,6 +309,10 @@
   </si>
   <si>
     <t>HpAdd</t>
+  </si>
+  <si>
+    <t>int32</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -779,7 +779,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
-    <col min="2" max="2" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="3" customWidth="1"/>
     <col min="3" max="3" width="16.375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.75" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.875" style="3" bestFit="1" customWidth="1"/>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2"/>
     </row>
@@ -818,61 +818,61 @@
         <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="R2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="S2" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="T2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:21" s="7" customFormat="1" ht="49.5" x14ac:dyDescent="0.3">
@@ -881,41 +881,41 @@
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R3" s="6"/>
       <c r="S3" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T3" s="6"/>
       <c r="U3" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
@@ -941,46 +941,46 @@
         <v>10</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="J4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
@@ -988,40 +988,40 @@
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>11</v>
@@ -1056,32 +1056,32 @@
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S6" s="8"/>
       <c r="T6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U6" s="8"/>
     </row>
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J7" s="8" t="b">
         <v>0</v>
@@ -1144,61 +1144,61 @@
         <v>8</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="K8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="M8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="N8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="Q8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="R8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="S8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="T8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="U8" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="U8" s="10" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
@@ -1206,10 +1206,10 @@
         <v>1001</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="F9" s="3">
         <v>30000</v>
@@ -1218,19 +1218,19 @@
         <v>1</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="Q9" s="3">
         <v>50</v>
@@ -1241,10 +1241,10 @@
         <v>2001</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="F10" s="3">
         <v>5000</v>
@@ -1253,19 +1253,19 @@
         <v>3</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="Q10" s="3">
         <v>-10</v>
@@ -1276,10 +1276,10 @@
         <v>2002</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3">
         <v>10000</v>
@@ -1288,19 +1288,19 @@
         <v>1</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M11" s="3">
         <v>2000</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O11" s="3">
         <v>30</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q11" s="3">
         <v>0</v>
@@ -1311,10 +1311,10 @@
         <v>1002</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F12" s="3">
         <v>8000</v>
@@ -1323,19 +1323,19 @@
         <v>1</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M12" s="3">
         <v>1000</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O12" s="3">
         <v>20</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q12" s="3">
         <v>100</v>
